--- a/artfynd/A 62137-2022 artfynd.xlsx
+++ b/artfynd/A 62137-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62137-2022 artfynd.xlsx
+++ b/artfynd/A 62137-2022 artfynd.xlsx
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100590548</v>
+        <v>115192420</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Huddunge, Upl</t>
+          <t>Huddungeby, Huddungeby, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610409.8779594492</v>
+        <v>610401</v>
       </c>
       <c r="R2" t="n">
-        <v>6659729.741469918</v>
+        <v>6659805</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,54 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100590612</v>
+        <v>102992352</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Huddunge, Upl</t>
+          <t>Huddungeby, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610405.7880586359</v>
+        <v>610423</v>
       </c>
       <c r="R3" t="n">
-        <v>6659732.616440299</v>
+        <v>6659719</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -866,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102992352</v>
+        <v>102992392</v>
       </c>
       <c r="B4" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610423.2226123706</v>
+        <v>610516</v>
       </c>
       <c r="R4" t="n">
-        <v>6659718.650743594</v>
+        <v>6659886</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -985,19 +954,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,43 +984,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102992376</v>
+        <v>102992367</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610480.6560944865</v>
+        <v>610471</v>
       </c>
       <c r="R5" t="n">
-        <v>6659839.281871743</v>
+        <v>6659740</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1102,19 +1055,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,53 +1085,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102992392</v>
+        <v>100590548</v>
       </c>
       <c r="B6" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Huddungeby, Upl</t>
+          <t>Huddunge, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610515.7909562342</v>
+        <v>610409</v>
       </c>
       <c r="R6" t="n">
-        <v>6659885.800522096</v>
+        <v>6659729</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1215,22 +1154,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,15 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102992384</v>
+        <v>100590612</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,14 +1222,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Huddungeby, Upl</t>
+          <t>Huddunge, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610497.1663545556</v>
+        <v>610406</v>
       </c>
       <c r="R7" t="n">
-        <v>6659872.751228397</v>
+        <v>6659733</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1332,22 +1256,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,42 +1289,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102992367</v>
+        <v>102992376</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610470.6087063326</v>
+        <v>610480</v>
       </c>
       <c r="R8" t="n">
-        <v>6659740.557382436</v>
+        <v>6659840</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1451,19 +1361,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,15 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102992428</v>
+        <v>102992384</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>610524.9307748607</v>
+        <v>610497</v>
       </c>
       <c r="R9" t="n">
-        <v>6659898.065345204</v>
+        <v>6659872</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1568,19 +1463,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,37 +1493,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102992462</v>
+        <v>102992428</v>
       </c>
       <c r="B10" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1652,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610463.3322209201</v>
+        <v>610525</v>
       </c>
       <c r="R10" t="n">
-        <v>6659866.239704687</v>
+        <v>6659898</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1685,19 +1565,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,15 +1595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115192343</v>
+        <v>115192064</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,14 +1626,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Huddungeby (Huddungeby), Upl</t>
+          <t>Huddungeby, Huddungeby, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610394</v>
+        <v>610451</v>
       </c>
       <c r="R11" t="n">
-        <v>6659786</v>
+        <v>6659696</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,7 +1665,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1675,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,15 +1702,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115192998</v>
+        <v>115192343</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,14 +1733,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Huddungeby (Huddungeby), Upl</t>
+          <t>Huddungeby, Huddungeby, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>610337</v>
+        <v>610394</v>
       </c>
       <c r="R12" t="n">
-        <v>6659984</v>
+        <v>6659786</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1912,7 +1772,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,7 +1782,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,15 +1809,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115192990</v>
+        <v>115192970</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,14 +1840,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Huddungeby (Huddungeby), Upl</t>
+          <t>Huddungeby, Huddungeby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>610351</v>
+        <v>610390</v>
       </c>
       <c r="R13" t="n">
-        <v>6659964</v>
+        <v>6659979</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2024,7 +1879,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2034,7 +1889,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,50 +1916,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115192420</v>
+        <v>115192990</v>
       </c>
       <c r="B14" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Huddungeby (Huddungeby), Upl</t>
+          <t>Huddungeby, Huddungeby, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>610401</v>
+        <v>610351</v>
       </c>
       <c r="R14" t="n">
-        <v>6659805</v>
+        <v>6659964</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2136,7 +1986,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +1996,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,15 +2023,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115192064</v>
+        <v>115192998</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,14 +2054,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Huddungeby (Huddungeby), Upl</t>
+          <t>Huddungeby, Huddungeby, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>610451</v>
+        <v>610337</v>
       </c>
       <c r="R15" t="n">
-        <v>6659696</v>
+        <v>6659984</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2248,7 +2093,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2258,7 +2103,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,53 +2130,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115192970</v>
+        <v>102992462</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Huddungeby (Huddungeby), Upl</t>
+          <t>Huddungeby, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>610390</v>
+        <v>610463</v>
       </c>
       <c r="R16" t="n">
-        <v>6659979</v>
+        <v>6659867</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,22 +2199,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:31</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:31</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,6 +2213,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62137-2022 artfynd.xlsx
+++ b/artfynd/A 62137-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115192420</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102992352</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102992392</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102992367</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590548</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590612</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102992376</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102992384</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102992428</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1699,6 +1749,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115192064</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,6 +1861,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115192343</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1913,6 +1973,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115192970</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2020,6 +2085,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115192990</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2127,6 +2197,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115192998</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2229,8 +2304,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102992462</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>